--- a/data/rr_table_quanti.xlsx
+++ b/data/rr_table_quanti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35B2348-40DD-2948-895F-4682DB19812F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC04EC3-D076-164E-8AC9-7C8BB84B7FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35140" yWindow="-2340" windowWidth="32720" windowHeight="19460" activeTab="2" xr2:uid="{8D5AF9D6-033C-0248-AC54-73E73626E3DE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" activeTab="1" xr2:uid="{8D5AF9D6-033C-0248-AC54-73E73626E3DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
